--- a/go/creeper/planilla.xlsx
+++ b/go/creeper/planilla.xlsx
@@ -54,4 +54,11 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=creeper_infection/.creeper_marker.txt>CREEPER VIRUS - INFECTION MARKER
+Timestamp: 2026-07-09 14:31:31
+Original file: planilla.xlsx
+This file was infected by the Creeper educational virus.
+
 </file>
--- a/go/creeper/planilla.xlsx
+++ b/go/creeper/planilla.xlsx
@@ -54,11 +54,4 @@
     </row>
   </sheetData>
 </worksheet>
-</file>
-
-<file path=creeper_infection/.creeper_marker.txt>CREEPER VIRUS - INFECTION MARKER
-Timestamp: 2026-07-09 14:31:31
-Original file: planilla.xlsx
-This file was infected by the Creeper educational virus.
-
 </file>